--- a/tools/importer/reports/import-industry-page.report.xlsx
+++ b/tools/importer/reports/import-industry-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1160" uniqueCount="645">
   <si>
     <t>_reportFile</t>
   </si>
@@ -169,13 +169,13 @@
     <t>en-us/lp/dt/automation-platform.report.json</t>
   </si>
   <si>
-    <t>["hero","hero","cards","cards","cards","cards","carousel"]</t>
+    <t>["hero","cards","cards","cards","cards","tabs","carousel"]</t>
   </si>
   <si>
     <t>en-us/lp/dt/automation-platform</t>
   </si>
   <si>
-    <t>2026-03-21T07:53:44.902Z</t>
+    <t>2026-03-22T08:40:23.237Z</t>
   </si>
   <si>
     <t>Dell Automation Platform | Dell USA</t>
@@ -283,13 +283,13 @@
     <t>en-us/lp/dt/customer-stories-city-of-amarillo-genai.report.json</t>
   </si>
   <si>
-    <t>["cards","cards"]</t>
+    <t>["hero","columns","columns","cards","cards","cards","cards","cards"]</t>
   </si>
   <si>
     <t>en-us/lp/dt/customer-stories-city-of-amarillo-genai</t>
   </si>
   <si>
-    <t>2026-03-21T17:55:10.576Z</t>
+    <t>2026-03-22T03:15:21.992Z</t>
   </si>
   <si>
     <t>City of Amarillo​ | Dell USA</t>
@@ -349,7 +349,7 @@
     <t>en-us/lp/dt/customer-stories-dauntless-xr</t>
   </si>
   <si>
-    <t>2026-03-21T17:56:39.022Z</t>
+    <t>2026-03-22T03:15:29.733Z</t>
   </si>
   <si>
     <t>Dauntless XR | Dell USA</t>
@@ -361,13 +361,13 @@
     <t>en-us/lp/dt/customer-stories-deloitte.report.json</t>
   </si>
   <si>
-    <t>["cards"]</t>
+    <t>["hero","hero","columns","columns","cards","cards","cards","cards"]</t>
   </si>
   <si>
     <t>en-us/lp/dt/customer-stories-deloitte</t>
   </si>
   <si>
-    <t>2026-03-21T17:53:05.120Z</t>
+    <t>2026-03-22T03:14:39.485Z</t>
   </si>
   <si>
     <t>Deloitte | Dell USA</t>
@@ -397,7 +397,7 @@
     <t>en-us/lp/dt/customer-stories-eaton</t>
   </si>
   <si>
-    <t>2026-03-21T18:01:53.922Z</t>
+    <t>2026-03-22T03:14:46.486Z</t>
   </si>
   <si>
     <t>Eaton | Dell USA</t>
@@ -460,7 +460,7 @@
     <t>en-us/lp/dt/customer-stories-f1soft-group</t>
   </si>
   <si>
-    <t>2026-03-21T17:57:01.985Z</t>
+    <t>2026-03-22T03:15:37.318Z</t>
   </si>
   <si>
     <t>F1Soft Group | Dell USA</t>
@@ -517,10 +517,13 @@
     <t>en-us/lp/dt/customer-stories-hopeworks.report.json</t>
   </si>
   <si>
+    <t>["hero","columns","columns","cards","cards","cards","cards"]</t>
+  </si>
+  <si>
     <t>en-us/lp/dt/customer-stories-hopeworks</t>
   </si>
   <si>
-    <t>2026-03-21T17:55:49.146Z</t>
+    <t>2026-03-22T03:14:53.746Z</t>
   </si>
   <si>
     <t>Hopeworks | Dell USA</t>
@@ -640,7 +643,7 @@
     <t>en-us/lp/dt/customer-stories-lowes</t>
   </si>
   <si>
-    <t>2026-03-21T17:53:57.718Z</t>
+    <t>2026-03-22T03:15:00.681Z</t>
   </si>
   <si>
     <t>Lowe's | Dell USA</t>
@@ -655,7 +658,7 @@
     <t>en-us/lp/dt/customer-stories-macquarie-cloud-services</t>
   </si>
   <si>
-    <t>2026-03-21T17:55:28.038Z</t>
+    <t>2026-03-22T03:15:07.400Z</t>
   </si>
   <si>
     <t>Macquarie Cloud Services | Dell USA</t>
@@ -673,7 +676,7 @@
     <t>en-us/lp/dt/customer-stories-maricopa-county-recorders-office</t>
   </si>
   <si>
-    <t>2026-03-21T17:59:00.403Z</t>
+    <t>2026-03-22T03:16:27.935Z</t>
   </si>
   <si>
     <t>Customer Stories | Dell USA</t>
@@ -781,7 +784,7 @@
     <t>en-us/lp/dt/customer-stories-naver-cloud</t>
   </si>
   <si>
-    <t>2026-03-21T17:56:46.260Z</t>
+    <t>2026-03-22T03:15:45.409Z</t>
   </si>
   <si>
     <t>NAVER Cloud | Dell USA</t>
@@ -889,7 +892,7 @@
     <t>en-us/lp/dt/customer-stories-palladium-hotel-group</t>
   </si>
   <si>
-    <t>2026-03-21T18:02:01.860Z</t>
+    <t>2026-03-22T03:15:14.606Z</t>
   </si>
   <si>
     <t>Palladium Hotel Group | Dell USA</t>
@@ -1009,7 +1012,7 @@
     <t>en-us/lp/dt/customer-stories-sandisk-corporation</t>
   </si>
   <si>
-    <t>2026-03-21T17:56:32.134Z</t>
+    <t>2026-03-22T03:15:52.400Z</t>
   </si>
   <si>
     <t>Sandisk Corporation | Dell USA</t>
@@ -1039,7 +1042,7 @@
     <t>en-us/lp/dt/customer-stories-sns-network</t>
   </si>
   <si>
-    <t>2026-03-21T18:01:39.263Z</t>
+    <t>2026-03-22T03:15:58.105Z</t>
   </si>
   <si>
     <t>SNS Network | Dell USA</t>
@@ -1111,10 +1114,13 @@
     <t>en-us/lp/dt/customer-stories-the-wellcome-sanger-institute.report.json</t>
   </si>
   <si>
+    <t>["hero","hero","columns","columns","cards","cards"]</t>
+  </si>
+  <si>
     <t>en-us/lp/dt/customer-stories-the-wellcome-sanger-institute</t>
   </si>
   <si>
-    <t>2026-03-21T17:55:34.875Z</t>
+    <t>2026-03-22T03:16:04.708Z</t>
   </si>
   <si>
     <t>The Wellcome Sanger Institute | Dell USA</t>
@@ -1132,7 +1138,7 @@
     <t>en-us/lp/dt/customer-stories-theguthrieclinic</t>
   </si>
   <si>
-    <t>2026-03-21T17:56:02.209Z</t>
+    <t>2026-03-22T06:55:13.319Z</t>
   </si>
   <si>
     <t>The Guthrie Clinic | Dell USA</t>
@@ -1147,7 +1153,7 @@
     <t>en-us/lp/dt/customer-stories-university-of-texas-athletics</t>
   </si>
   <si>
-    <t>2026-03-21T17:53:21.234Z</t>
+    <t>2026-03-22T03:16:12.143Z</t>
   </si>
   <si>
     <t>University of Texas Athletics | Dell USA</t>
@@ -1288,7 +1294,7 @@
     <t>en-us/lp/dt/industry-energy.report.json</t>
   </si>
   <si>
-    <t>["hero","hero","hero","hero","carousel","carousel","carousel","carousel","cards","cards","cards","cards","cards","accordion"]</t>
+    <t>["hero","hero","hero","hero","carousel","carousel","carousel","carousel","cards","cards","cards","cards","cards","tabs","tabs","accordion"]</t>
   </si>
   <si>
     <t>en-us/lp/dt/industry-energy</t>
@@ -1297,7 +1303,7 @@
     <t>industry-page</t>
   </si>
   <si>
-    <t>2026-03-21T18:06:33.359Z</t>
+    <t>2026-03-22T20:51:30.905Z</t>
   </si>
   <si>
     <t>Energy | Dell USA</t>
@@ -1315,7 +1321,7 @@
     <t>en-us/lp/dt/industry-federal-government-it</t>
   </si>
   <si>
-    <t>2026-03-21T18:06:41.600Z</t>
+    <t>2026-03-22T20:51:39.978Z</t>
   </si>
   <si>
     <t>Dell Technologies Federal​ | Dell USA</t>
@@ -1333,7 +1339,7 @@
     <t>en-us/lp/dt/industry-financial-services</t>
   </si>
   <si>
-    <t>2026-03-21T18:06:48.571Z</t>
+    <t>2026-03-22T20:51:47.854Z</t>
   </si>
   <si>
     <t>Transforming the Financial Services Industry | Dell USA</t>
@@ -1351,7 +1357,7 @@
     <t>en-us/lp/dt/industry-healthcare</t>
   </si>
   <si>
-    <t>2026-03-21T18:06:24.998Z</t>
+    <t>2026-03-22T20:51:21.906Z</t>
   </si>
   <si>
     <t>Healthcare | Dell USA</t>
@@ -1363,13 +1369,13 @@
     <t>en-us/lp/dt/industry-higher-ed.report.json</t>
   </si>
   <si>
-    <t>["hero","hero","hero","cards","cards"]</t>
+    <t>["hero","hero","hero","cards","cards","tabs","tabs","tabs","tabs"]</t>
   </si>
   <si>
     <t>en-us/lp/dt/industry-higher-ed</t>
   </si>
   <si>
-    <t>2026-03-21T18:06:57.300Z</t>
+    <t>2026-03-22T20:51:57.912Z</t>
   </si>
   <si>
     <t>Higher Education IT Solutions | Dell USA</t>
@@ -1381,10 +1387,13 @@
     <t>en-us/lp/dt/industry-k12-ed.report.json</t>
   </si>
   <si>
+    <t>["hero","cards","cards","tabs","tabs"]</t>
+  </si>
+  <si>
     <t>en-us/lp/dt/industry-k12-ed</t>
   </si>
   <si>
-    <t>2026-03-21T18:07:04.209Z</t>
+    <t>2026-03-22T20:52:07.371Z</t>
   </si>
   <si>
     <t>K-12 IT Solutions | Dell USA</t>
@@ -1402,7 +1411,7 @@
     <t>en-us/lp/dt/industry-life-sciences</t>
   </si>
   <si>
-    <t>2026-03-21T18:07:11.620Z</t>
+    <t>2026-03-22T20:52:15.627Z</t>
   </si>
   <si>
     <t>Life Sciences | Dell USA</t>
@@ -1417,7 +1426,7 @@
     <t>en-us/lp/dt/industry-manufacturing</t>
   </si>
   <si>
-    <t>2026-03-21T18:07:19.816Z</t>
+    <t>2026-03-22T20:52:25.431Z</t>
   </si>
   <si>
     <t>Manufacturing | Dell USA</t>
@@ -1432,7 +1441,7 @@
     <t>en-us/lp/dt/industry-retail</t>
   </si>
   <si>
-    <t>2026-03-21T18:07:28.145Z</t>
+    <t>2026-03-22T20:52:35.686Z</t>
   </si>
   <si>
     <t>Retail | Dell USA</t>
@@ -1450,7 +1459,7 @@
     <t>en-us/lp/dt/industry-safety-security</t>
   </si>
   <si>
-    <t>2026-03-21T18:07:35.394Z</t>
+    <t>2026-03-22T20:52:41.976Z</t>
   </si>
   <si>
     <t>Safety &amp; Security Solutions - Video Storage Analytics | Dell USA</t>
@@ -1462,13 +1471,13 @@
     <t>en-us/lp/dt/industry-smart-cities.report.json</t>
   </si>
   <si>
-    <t>["hero","hero","cards","columns","accordion","accordion"]</t>
+    <t>["hero","hero","cards","columns","tabs","accordion","accordion"]</t>
   </si>
   <si>
     <t>en-us/lp/dt/industry-smart-cities</t>
   </si>
   <si>
-    <t>2026-03-21T18:07:42.865Z</t>
+    <t>2026-03-22T20:52:50.952Z</t>
   </si>
   <si>
     <t>Defining the digital future of our cities | Dell USA</t>
@@ -1480,13 +1489,13 @@
     <t>en-us/lp/dt/industry-state-and-local-government.report.json</t>
   </si>
   <si>
-    <t>["hero","hero","hero","carousel","cards","cards","cards","cards"]</t>
+    <t>["hero","hero","hero","carousel","cards","cards","cards","cards","tabs"]</t>
   </si>
   <si>
     <t>en-us/lp/dt/industry-state-and-local-government</t>
   </si>
   <si>
-    <t>2026-03-21T18:07:50.845Z</t>
+    <t>2026-03-22T20:52:58.628Z</t>
   </si>
   <si>
     <t>State and Local Government | Dell USA</t>
@@ -1498,13 +1507,13 @@
     <t>en-us/lp/dt/industry-telecom.report.json</t>
   </si>
   <si>
-    <t>["hero","hero","hero","hero","hero","cards","cards","cards","cards","cards","cards","columns","columns","columns"]</t>
+    <t>["hero","hero","hero","hero","hero","cards","cards","cards","cards","cards","cards","columns","columns","columns","tabs","tabs"]</t>
   </si>
   <si>
     <t>en-us/lp/dt/industry-telecom</t>
   </si>
   <si>
-    <t>2026-03-21T18:07:57.086Z</t>
+    <t>2026-03-22T20:53:05.391Z</t>
   </si>
   <si>
     <t>Telecom Solutions | Dell USA</t>
@@ -2582,7 +2591,7 @@
         <v>14</v>
       </c>
       <c r="G8" t="s">
-        <v>47</v>
+        <v>15</v>
       </c>
       <c r="H8" t="s">
         <v>54</v>
@@ -3271,7 +3280,7 @@
         <v>167</v>
       </c>
       <c r="B30" t="s">
-        <v>116</v>
+        <v>168</v>
       </c>
       <c r="C30" t="s">
         <v>12</v>
@@ -3280,7 +3289,7 @@
         <v>12</v>
       </c>
       <c r="E30" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F30" t="s">
         <v>14</v>
@@ -3289,18 +3298,18 @@
         <v>60</v>
       </c>
       <c r="H30" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="I30" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J30" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B31" t="s">
         <v>58</v>
@@ -3312,7 +3321,7 @@
         <v>12</v>
       </c>
       <c r="E31" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F31" t="s">
         <v>14</v>
@@ -3321,18 +3330,18 @@
         <v>60</v>
       </c>
       <c r="H31" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="I31" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="J31" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B32" t="s">
         <v>58</v>
@@ -3344,7 +3353,7 @@
         <v>12</v>
       </c>
       <c r="E32" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F32" t="s">
         <v>14</v>
@@ -3353,18 +3362,18 @@
         <v>60</v>
       </c>
       <c r="H32" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="I32" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="J32" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B33" t="s">
         <v>58</v>
@@ -3376,7 +3385,7 @@
         <v>12</v>
       </c>
       <c r="E33" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F33" t="s">
         <v>14</v>
@@ -3385,18 +3394,18 @@
         <v>60</v>
       </c>
       <c r="H33" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="I33" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J33" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B34" t="s">
         <v>58</v>
@@ -3408,7 +3417,7 @@
         <v>12</v>
       </c>
       <c r="E34" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F34" t="s">
         <v>14</v>
@@ -3417,18 +3426,18 @@
         <v>60</v>
       </c>
       <c r="H34" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="I34" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J34" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B35" t="s">
         <v>58</v>
@@ -3440,7 +3449,7 @@
         <v>12</v>
       </c>
       <c r="E35" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F35" t="s">
         <v>14</v>
@@ -3449,18 +3458,18 @@
         <v>60</v>
       </c>
       <c r="H35" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="I35" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J35" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B36" t="s">
         <v>58</v>
@@ -3472,7 +3481,7 @@
         <v>12</v>
       </c>
       <c r="E36" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F36" t="s">
         <v>14</v>
@@ -3481,18 +3490,18 @@
         <v>60</v>
       </c>
       <c r="H36" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="I36" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="J36" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B37" t="s">
         <v>58</v>
@@ -3504,7 +3513,7 @@
         <v>12</v>
       </c>
       <c r="E37" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F37" t="s">
         <v>14</v>
@@ -3513,18 +3522,18 @@
         <v>60</v>
       </c>
       <c r="H37" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="I37" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="J37" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B38" t="s">
         <v>90</v>
@@ -3536,7 +3545,7 @@
         <v>12</v>
       </c>
       <c r="E38" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="F38" t="s">
         <v>14</v>
@@ -3545,18 +3554,18 @@
         <v>60</v>
       </c>
       <c r="H38" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="I38" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J38" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B39" t="s">
         <v>116</v>
@@ -3568,7 +3577,7 @@
         <v>12</v>
       </c>
       <c r="E39" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F39" t="s">
         <v>14</v>
@@ -3577,21 +3586,21 @@
         <v>60</v>
       </c>
       <c r="H39" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="I39" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="J39" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B40" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C40" t="s">
         <v>12</v>
@@ -3600,7 +3609,7 @@
         <v>12</v>
       </c>
       <c r="E40" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F40" t="s">
         <v>14</v>
@@ -3609,18 +3618,18 @@
         <v>60</v>
       </c>
       <c r="H40" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I40" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="J40" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B41" t="s">
         <v>58</v>
@@ -3632,7 +3641,7 @@
         <v>12</v>
       </c>
       <c r="E41" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F41" t="s">
         <v>14</v>
@@ -3641,18 +3650,18 @@
         <v>60</v>
       </c>
       <c r="H41" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="I41" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J41" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B42" t="s">
         <v>58</v>
@@ -3664,7 +3673,7 @@
         <v>12</v>
       </c>
       <c r="E42" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F42" t="s">
         <v>14</v>
@@ -3673,18 +3682,18 @@
         <v>60</v>
       </c>
       <c r="H42" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="I42" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J42" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="43" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B43" t="s">
         <v>58</v>
@@ -3696,7 +3705,7 @@
         <v>12</v>
       </c>
       <c r="E43" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="F43" t="s">
         <v>14</v>
@@ -3705,21 +3714,21 @@
         <v>60</v>
       </c>
       <c r="H43" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="I43" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="J43" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B44" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C44" t="s">
         <v>12</v>
@@ -3728,7 +3737,7 @@
         <v>12</v>
       </c>
       <c r="E44" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F44" t="s">
         <v>14</v>
@@ -3737,18 +3746,18 @@
         <v>60</v>
       </c>
       <c r="H44" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="I44" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="J44" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B45" t="s">
         <v>58</v>
@@ -3760,7 +3769,7 @@
         <v>12</v>
       </c>
       <c r="E45" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F45" t="s">
         <v>14</v>
@@ -3769,18 +3778,18 @@
         <v>60</v>
       </c>
       <c r="H45" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I45" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J45" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B46" t="s">
         <v>58</v>
@@ -3792,7 +3801,7 @@
         <v>12</v>
       </c>
       <c r="E46" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="F46" t="s">
         <v>14</v>
@@ -3801,18 +3810,18 @@
         <v>60</v>
       </c>
       <c r="H46" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="I46" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="J46" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B47" t="s">
         <v>90</v>
@@ -3824,7 +3833,7 @@
         <v>12</v>
       </c>
       <c r="E47" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="F47" t="s">
         <v>14</v>
@@ -3833,18 +3842,18 @@
         <v>60</v>
       </c>
       <c r="H47" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="I47" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="J47" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B48" t="s">
         <v>58</v>
@@ -3856,7 +3865,7 @@
         <v>12</v>
       </c>
       <c r="E48" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="F48" t="s">
         <v>14</v>
@@ -3865,18 +3874,18 @@
         <v>60</v>
       </c>
       <c r="H48" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="I48" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="J48" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B49" t="s">
         <v>58</v>
@@ -3888,7 +3897,7 @@
         <v>12</v>
       </c>
       <c r="E49" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="F49" t="s">
         <v>14</v>
@@ -3897,21 +3906,21 @@
         <v>60</v>
       </c>
       <c r="H49" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="I49" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="J49" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B50" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C50" t="s">
         <v>12</v>
@@ -3920,7 +3929,7 @@
         <v>12</v>
       </c>
       <c r="E50" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="F50" t="s">
         <v>14</v>
@@ -3929,18 +3938,18 @@
         <v>60</v>
       </c>
       <c r="H50" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="I50" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="J50" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B51" t="s">
         <v>58</v>
@@ -3952,7 +3961,7 @@
         <v>12</v>
       </c>
       <c r="E51" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F51" t="s">
         <v>14</v>
@@ -3961,18 +3970,18 @@
         <v>60</v>
       </c>
       <c r="H51" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="I51" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="J51" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B52" t="s">
         <v>58</v>
@@ -3984,7 +3993,7 @@
         <v>12</v>
       </c>
       <c r="E52" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F52" t="s">
         <v>14</v>
@@ -3993,18 +4002,18 @@
         <v>60</v>
       </c>
       <c r="H52" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="I52" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J52" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B53" t="s">
         <v>58</v>
@@ -4016,7 +4025,7 @@
         <v>12</v>
       </c>
       <c r="E53" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="F53" t="s">
         <v>14</v>
@@ -4025,18 +4034,18 @@
         <v>60</v>
       </c>
       <c r="H53" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="I53" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="J53" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B54" t="s">
         <v>116</v>
@@ -4048,7 +4057,7 @@
         <v>12</v>
       </c>
       <c r="E54" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F54" t="s">
         <v>14</v>
@@ -4057,18 +4066,18 @@
         <v>60</v>
       </c>
       <c r="H54" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="I54" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="J54" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B55" t="s">
         <v>58</v>
@@ -4080,7 +4089,7 @@
         <v>12</v>
       </c>
       <c r="E55" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="F55" t="s">
         <v>14</v>
@@ -4089,18 +4098,18 @@
         <v>60</v>
       </c>
       <c r="H55" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="I55" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J55" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B56" t="s">
         <v>58</v>
@@ -4112,7 +4121,7 @@
         <v>12</v>
       </c>
       <c r="E56" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F56" t="s">
         <v>14</v>
@@ -4121,18 +4130,18 @@
         <v>60</v>
       </c>
       <c r="H56" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="I56" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="J56" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B57" t="s">
         <v>58</v>
@@ -4144,7 +4153,7 @@
         <v>12</v>
       </c>
       <c r="E57" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F57" t="s">
         <v>14</v>
@@ -4153,18 +4162,18 @@
         <v>60</v>
       </c>
       <c r="H57" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="I57" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J57" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B58" t="s">
         <v>58</v>
@@ -4176,7 +4185,7 @@
         <v>12</v>
       </c>
       <c r="E58" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F58" t="s">
         <v>14</v>
@@ -4185,18 +4194,18 @@
         <v>60</v>
       </c>
       <c r="H58" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="I58" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="J58" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B59" t="s">
         <v>58</v>
@@ -4208,7 +4217,7 @@
         <v>12</v>
       </c>
       <c r="E59" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="F59" t="s">
         <v>14</v>
@@ -4217,18 +4226,18 @@
         <v>60</v>
       </c>
       <c r="H59" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I59" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J59" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B60" t="s">
         <v>58</v>
@@ -4240,7 +4249,7 @@
         <v>12</v>
       </c>
       <c r="E60" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F60" t="s">
         <v>14</v>
@@ -4249,18 +4258,18 @@
         <v>60</v>
       </c>
       <c r="H60" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="I60" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="J60" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B61" t="s">
         <v>58</v>
@@ -4272,7 +4281,7 @@
         <v>12</v>
       </c>
       <c r="E61" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F61" t="s">
         <v>14</v>
@@ -4281,18 +4290,18 @@
         <v>60</v>
       </c>
       <c r="H61" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="I61" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J61" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B62" t="s">
         <v>90</v>
@@ -4304,7 +4313,7 @@
         <v>12</v>
       </c>
       <c r="E62" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F62" t="s">
         <v>14</v>
@@ -4313,18 +4322,18 @@
         <v>60</v>
       </c>
       <c r="H62" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="I62" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="J62" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="B63" t="s">
         <v>58</v>
@@ -4336,7 +4345,7 @@
         <v>12</v>
       </c>
       <c r="E63" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="F63" t="s">
         <v>14</v>
@@ -4345,18 +4354,18 @@
         <v>60</v>
       </c>
       <c r="H63" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="I63" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="J63" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B64" t="s">
         <v>90</v>
@@ -4368,7 +4377,7 @@
         <v>12</v>
       </c>
       <c r="E64" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F64" t="s">
         <v>14</v>
@@ -4377,18 +4386,18 @@
         <v>60</v>
       </c>
       <c r="H64" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="I64" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J64" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B65" t="s">
         <v>58</v>
@@ -4400,7 +4409,7 @@
         <v>12</v>
       </c>
       <c r="E65" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="F65" t="s">
         <v>14</v>
@@ -4409,18 +4418,18 @@
         <v>60</v>
       </c>
       <c r="H65" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="I65" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="J65" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B66" t="s">
         <v>58</v>
@@ -4432,7 +4441,7 @@
         <v>12</v>
       </c>
       <c r="E66" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="F66" t="s">
         <v>14</v>
@@ -4441,18 +4450,18 @@
         <v>60</v>
       </c>
       <c r="H66" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="I66" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="J66" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B67" t="s">
         <v>58</v>
@@ -4464,7 +4473,7 @@
         <v>12</v>
       </c>
       <c r="E67" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="F67" t="s">
         <v>14</v>
@@ -4473,21 +4482,21 @@
         <v>60</v>
       </c>
       <c r="H67" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="I67" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J67" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="68" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B68" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C68" t="s">
         <v>12</v>
@@ -4496,7 +4505,7 @@
         <v>12</v>
       </c>
       <c r="E68" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F68" t="s">
         <v>14</v>
@@ -4505,21 +4514,21 @@
         <v>60</v>
       </c>
       <c r="H68" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="I68" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="J68" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="69" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B69" t="s">
-        <v>116</v>
+        <v>367</v>
       </c>
       <c r="C69" t="s">
         <v>12</v>
@@ -4528,7 +4537,7 @@
         <v>12</v>
       </c>
       <c r="E69" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="F69" t="s">
         <v>14</v>
@@ -4537,21 +4546,21 @@
         <v>60</v>
       </c>
       <c r="H69" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="I69" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="J69" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B70" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C70" t="s">
         <v>12</v>
@@ -4560,7 +4569,7 @@
         <v>12</v>
       </c>
       <c r="E70" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="F70" t="s">
         <v>14</v>
@@ -4569,18 +4578,18 @@
         <v>60</v>
       </c>
       <c r="H70" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="I70" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="J70" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B71" t="s">
         <v>90</v>
@@ -4592,7 +4601,7 @@
         <v>12</v>
       </c>
       <c r="E71" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F71" t="s">
         <v>14</v>
@@ -4601,18 +4610,18 @@
         <v>60</v>
       </c>
       <c r="H71" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="I71" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="J71" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="B72" t="s">
         <v>58</v>
@@ -4624,7 +4633,7 @@
         <v>12</v>
       </c>
       <c r="E72" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F72" t="s">
         <v>14</v>
@@ -4633,18 +4642,18 @@
         <v>60</v>
       </c>
       <c r="H72" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I72" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="J72" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B73" t="s">
         <v>58</v>
@@ -4656,7 +4665,7 @@
         <v>12</v>
       </c>
       <c r="E73" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="F73" t="s">
         <v>14</v>
@@ -4665,18 +4674,18 @@
         <v>60</v>
       </c>
       <c r="H73" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="I73" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="J73" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B74" t="s">
         <v>58</v>
@@ -4688,7 +4697,7 @@
         <v>12</v>
       </c>
       <c r="E74" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="F74" t="s">
         <v>14</v>
@@ -4697,18 +4706,18 @@
         <v>60</v>
       </c>
       <c r="H74" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="I74" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="J74" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B75" t="s">
         <v>58</v>
@@ -4720,7 +4729,7 @@
         <v>12</v>
       </c>
       <c r="E75" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F75" t="s">
         <v>14</v>
@@ -4729,18 +4738,18 @@
         <v>60</v>
       </c>
       <c r="H75" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="I75" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="J75" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="76" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B76" t="s">
         <v>58</v>
@@ -4752,7 +4761,7 @@
         <v>12</v>
       </c>
       <c r="E76" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F76" t="s">
         <v>14</v>
@@ -4761,21 +4770,21 @@
         <v>60</v>
       </c>
       <c r="H76" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="I76" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="J76" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B77" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="C77" t="s">
         <v>12</v>
@@ -4784,7 +4793,7 @@
         <v>12</v>
       </c>
       <c r="E77" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="F77" t="s">
         <v>14</v>
@@ -4793,21 +4802,21 @@
         <v>47</v>
       </c>
       <c r="H77" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="I77" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="J77" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="78" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B78" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C78" t="s">
         <v>12</v>
@@ -4816,7 +4825,7 @@
         <v>12</v>
       </c>
       <c r="E78" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="F78" t="s">
         <v>14</v>
@@ -4825,21 +4834,21 @@
         <v>28</v>
       </c>
       <c r="H78" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="I78" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="J78" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="B79" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C79" t="s">
         <v>12</v>
@@ -4848,7 +4857,7 @@
         <v>12</v>
       </c>
       <c r="E79" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F79" t="s">
         <v>14</v>
@@ -4857,21 +4866,21 @@
         <v>28</v>
       </c>
       <c r="H79" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="I79" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="J79" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B80" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C80" t="s">
         <v>12</v>
@@ -4880,30 +4889,30 @@
         <v>12</v>
       </c>
       <c r="E80" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="F80" t="s">
         <v>14</v>
       </c>
       <c r="G80" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H80" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="I80" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="J80" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B81" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="C81" t="s">
         <v>12</v>
@@ -4912,30 +4921,30 @@
         <v>12</v>
       </c>
       <c r="E81" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F81" t="s">
         <v>14</v>
       </c>
       <c r="G81" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H81" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="I81" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="J81" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B82" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C82" t="s">
         <v>12</v>
@@ -4944,30 +4953,30 @@
         <v>12</v>
       </c>
       <c r="E82" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="F82" t="s">
         <v>14</v>
       </c>
       <c r="G82" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H82" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="I82" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="J82" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B83" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C83" t="s">
         <v>12</v>
@@ -4976,30 +4985,30 @@
         <v>12</v>
       </c>
       <c r="E83" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F83" t="s">
         <v>14</v>
       </c>
       <c r="G83" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H83" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="I83" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="J83" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B84" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C84" t="s">
         <v>12</v>
@@ -5008,30 +5017,30 @@
         <v>12</v>
       </c>
       <c r="E84" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="F84" t="s">
         <v>14</v>
       </c>
       <c r="G84" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H84" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="I84" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="J84" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B85" t="s">
-        <v>371</v>
+        <v>458</v>
       </c>
       <c r="C85" t="s">
         <v>12</v>
@@ -5040,30 +5049,30 @@
         <v>12</v>
       </c>
       <c r="E85" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="F85" t="s">
         <v>14</v>
       </c>
       <c r="G85" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H85" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="I85" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="J85" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="86" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="B86" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C86" t="s">
         <v>12</v>
@@ -5072,30 +5081,30 @@
         <v>12</v>
       </c>
       <c r="E86" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="F86" t="s">
         <v>14</v>
       </c>
       <c r="G86" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H86" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="I86" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="J86" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="87" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B87" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C87" t="s">
         <v>12</v>
@@ -5104,30 +5113,30 @@
         <v>12</v>
       </c>
       <c r="E87" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="F87" t="s">
         <v>14</v>
       </c>
       <c r="G87" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H87" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="I87" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="J87" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="B88" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="C88" t="s">
         <v>12</v>
@@ -5136,30 +5145,30 @@
         <v>12</v>
       </c>
       <c r="E88" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="F88" t="s">
         <v>14</v>
       </c>
       <c r="G88" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H88" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="I88" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="J88" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B89" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="C89" t="s">
         <v>12</v>
@@ -5168,30 +5177,30 @@
         <v>12</v>
       </c>
       <c r="E89" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="F89" t="s">
         <v>14</v>
       </c>
       <c r="G89" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H89" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="I89" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="J89" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B90" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="C90" t="s">
         <v>12</v>
@@ -5200,30 +5209,30 @@
         <v>12</v>
       </c>
       <c r="E90" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="F90" t="s">
         <v>14</v>
       </c>
       <c r="G90" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H90" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="I90" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="J90" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
       <c r="B91" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="C91" t="s">
         <v>12</v>
@@ -5232,30 +5241,30 @@
         <v>12</v>
       </c>
       <c r="E91" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="F91" t="s">
         <v>14</v>
       </c>
       <c r="G91" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H91" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="I91" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="J91" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="B92" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="C92" t="s">
         <v>12</v>
@@ -5264,30 +5273,30 @@
         <v>12</v>
       </c>
       <c r="E92" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="F92" t="s">
         <v>14</v>
       </c>
       <c r="G92" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H92" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="I92" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="J92" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="93" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="B93" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C93" t="s">
         <v>12</v>
@@ -5296,30 +5305,30 @@
         <v>12</v>
       </c>
       <c r="E93" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="F93" t="s">
         <v>14</v>
       </c>
       <c r="G93" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="H93" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="I93" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="J93" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="94" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="B94" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C94" t="s">
         <v>12</v>
@@ -5328,7 +5337,7 @@
         <v>12</v>
       </c>
       <c r="E94" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="F94" t="s">
         <v>14</v>
@@ -5337,21 +5346,21 @@
         <v>47</v>
       </c>
       <c r="H94" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="I94" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="J94" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="95" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B95" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="C95" t="s">
         <v>12</v>
@@ -5360,7 +5369,7 @@
         <v>12</v>
       </c>
       <c r="E95" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="F95" t="s">
         <v>14</v>
@@ -5369,21 +5378,21 @@
         <v>47</v>
       </c>
       <c r="H95" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="I95" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="J95" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
     <row r="96" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="B96" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="C96" t="s">
         <v>12</v>
@@ -5392,7 +5401,7 @@
         <v>12</v>
       </c>
       <c r="E96" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="F96" t="s">
         <v>14</v>
@@ -5401,21 +5410,21 @@
         <v>47</v>
       </c>
       <c r="H96" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="I96" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="J96" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
     </row>
     <row r="97" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="B97" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="C97" t="s">
         <v>12</v>
@@ -5424,7 +5433,7 @@
         <v>12</v>
       </c>
       <c r="E97" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="F97" t="s">
         <v>14</v>
@@ -5433,21 +5442,21 @@
         <v>28</v>
       </c>
       <c r="H97" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="I97" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="J97" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
     </row>
     <row r="98" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B98" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="C98" t="s">
         <v>12</v>
@@ -5456,30 +5465,30 @@
         <v>12</v>
       </c>
       <c r="E98" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="F98" t="s">
         <v>14</v>
       </c>
       <c r="G98" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="H98" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="I98" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="J98" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
     </row>
     <row r="99" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="B99" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="C99" t="s">
         <v>12</v>
@@ -5488,7 +5497,7 @@
         <v>12</v>
       </c>
       <c r="E99" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="F99" t="s">
         <v>14</v>
@@ -5497,21 +5506,21 @@
         <v>47</v>
       </c>
       <c r="H99" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="I99" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="J99" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="B100" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="C100" t="s">
         <v>12</v>
@@ -5520,7 +5529,7 @@
         <v>12</v>
       </c>
       <c r="E100" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="F100" t="s">
         <v>14</v>
@@ -5529,21 +5538,21 @@
         <v>47</v>
       </c>
       <c r="H100" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="I100" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="J100" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="B101" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="C101" t="s">
         <v>12</v>
@@ -5552,30 +5561,30 @@
         <v>12</v>
       </c>
       <c r="E101" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="F101" t="s">
         <v>14</v>
       </c>
       <c r="G101" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="H101" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="I101" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="J101" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
     </row>
     <row r="102" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="B102" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="C102" t="s">
         <v>12</v>
@@ -5584,7 +5593,7 @@
         <v>12</v>
       </c>
       <c r="E102" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="F102" t="s">
         <v>14</v>
@@ -5593,21 +5602,21 @@
         <v>47</v>
       </c>
       <c r="H102" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="I102" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="J102" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
     </row>
     <row r="103" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="B103" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="C103" t="s">
         <v>12</v>
@@ -5616,7 +5625,7 @@
         <v>12</v>
       </c>
       <c r="E103" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="F103" t="s">
         <v>14</v>
@@ -5625,18 +5634,18 @@
         <v>47</v>
       </c>
       <c r="H103" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="I103" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="J103" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
     </row>
     <row r="104" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="B104" t="s">
         <v>137</v>
@@ -5648,7 +5657,7 @@
         <v>12</v>
       </c>
       <c r="E104" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="F104" t="s">
         <v>14</v>
@@ -5657,21 +5666,21 @@
         <v>47</v>
       </c>
       <c r="H104" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="I104" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="J104" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
     </row>
     <row r="105" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="B105" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C105" t="s">
         <v>12</v>
@@ -5680,30 +5689,30 @@
         <v>12</v>
       </c>
       <c r="E105" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="F105" t="s">
         <v>14</v>
       </c>
       <c r="G105" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="H105" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="I105" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="J105" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
     </row>
     <row r="106" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="B106" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C106" t="s">
         <v>12</v>
@@ -5712,30 +5721,30 @@
         <v>12</v>
       </c>
       <c r="E106" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="F106" t="s">
         <v>14</v>
       </c>
       <c r="G106" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="H106" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="I106" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="J106" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
     </row>
     <row r="107" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="B107" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C107" t="s">
         <v>12</v>
@@ -5744,30 +5753,30 @@
         <v>12</v>
       </c>
       <c r="E107" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="F107" t="s">
         <v>14</v>
       </c>
       <c r="G107" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="H107" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="I107" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="J107" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="B108" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="C108" t="s">
         <v>12</v>
@@ -5776,30 +5785,30 @@
         <v>12</v>
       </c>
       <c r="E108" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="F108" t="s">
         <v>14</v>
       </c>
       <c r="G108" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="H108" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="I108" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="J108" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="B109" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="C109" t="s">
         <v>12</v>
@@ -5808,62 +5817,62 @@
         <v>12</v>
       </c>
       <c r="E109" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="F109" t="s">
         <v>14</v>
       </c>
       <c r="G109" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="H109" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="I109" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="J109" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
     </row>
     <row r="110" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="B110" t="s">
         <v>12</v>
       </c>
       <c r="C110" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="D110" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="E110" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="F110" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="G110" t="s">
         <v>12</v>
       </c>
       <c r="H110" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="I110" t="s">
         <v>12</v>
       </c>
       <c r="J110" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="B111" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="C111" t="s">
         <v>12</v>
@@ -5872,30 +5881,30 @@
         <v>12</v>
       </c>
       <c r="E111" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="F111" t="s">
         <v>14</v>
       </c>
       <c r="G111" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="H111" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="I111" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="J111" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="B112" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C112" t="s">
         <v>12</v>
@@ -5904,30 +5913,30 @@
         <v>12</v>
       </c>
       <c r="E112" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="F112" t="s">
         <v>14</v>
       </c>
       <c r="G112" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="H112" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="I112" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="J112" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
     </row>
     <row r="113" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="B113" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="C113" t="s">
         <v>12</v>
@@ -5936,30 +5945,30 @@
         <v>12</v>
       </c>
       <c r="E113" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="F113" t="s">
         <v>14</v>
       </c>
       <c r="G113" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="H113" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="I113" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="J113" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
     </row>
     <row r="114" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="B114" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="C114" t="s">
         <v>12</v>
@@ -5968,30 +5977,30 @@
         <v>12</v>
       </c>
       <c r="E114" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="F114" t="s">
         <v>14</v>
       </c>
       <c r="G114" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="H114" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="I114" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="J114" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="B115" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C115" t="s">
         <v>12</v>
@@ -6000,30 +6009,30 @@
         <v>12</v>
       </c>
       <c r="E115" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="F115" t="s">
         <v>14</v>
       </c>
       <c r="G115" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="H115" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="I115" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="J115" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
     </row>
     <row r="116" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="B116" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="C116" t="s">
         <v>12</v>
@@ -6032,22 +6041,22 @@
         <v>12</v>
       </c>
       <c r="E116" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="F116" t="s">
         <v>14</v>
       </c>
       <c r="G116" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="H116" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="I116" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="J116" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
     </row>
   </sheetData>
